--- a/TASK2/Scenariji/SC03_RezervacijaGrupnogTreninga.xlsx
+++ b/TASK2/Scenariji/SC03_RezervacijaGrupnogTreninga.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clan pregledava raspored grupnih treninga i rezervise mjesto na zeljenom treningu.</t>
+          <t>Član pregledava raspored grupnih treninga i rezervise mjesto na željenom treningu.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Provjera kapaciteta treninga prilikom rezervacije; Otkazivanje rezervacije najkasnije 2 sata prije pocetka</t>
+          <t>Provjera kapaciteta treninga prilikom rezervacije; Otkazivanje rezervacije najkasnije 2 sata prije početka</t>
         </is>
       </c>
     </row>
@@ -497,14 +497,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Clan je prijavljen na sistem. Clan ima aktivnu clanarinu.</t>
+          <t>Član je prijavljen na sistem. Član ima aktivnu članarinu.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - uspjesan zavrsetak</t>
+          <t>Posljedice - uspješan završetak</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -516,12 +516,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Posljedice - neuspjesan zavrsetak</t>
+          <t>Posljedice - neuspješan završetak</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Rezervacija nije kreirana zbog neaktivne clanarine ili popunjenosti.</t>
+          <t>Rezervacija nije kreirana zbog neaktivne članarine ili popunjenosti.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Clan pregledava raspored, bira trening, sistem provjerava uslove i kreira rezervaciju.</t>
+          <t>Član pregledava raspored, bira trening, sistem provjerava uslove i kreira rezervaciju.</t>
         </is>
       </c>
     </row>
@@ -569,10 +569,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Nema aktivne clanarine, Nema slobodnih mjesta</t>
-        </is>
-      </c>
-    </row>
+          <t>Nema aktivne članarine, Nema slobodnih mjesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -583,7 +584,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -630,7 +631,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>6. Provjera da li clan ima aktivnu clanarinu</t>
+          <t>6. Provjera da li član ima aktivnu članarinu</t>
         </is>
       </c>
     </row>
@@ -655,17 +656,18 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Alternativni Tok - Nema aktivne clanarine</t>
+          <t>Alternativni Tok - Nema aktivne članarine</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -677,7 +679,7 @@
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>6a. Sistem detektuje da clan nema aktivnu clanarinu</t>
+          <t>6a. Sistem detektuje da član nema aktivnu članarinu</t>
         </is>
       </c>
     </row>
@@ -691,17 +693,18 @@
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>6c. Ponuda opcije kupovine clanarine</t>
+          <t>6c. Ponuda opcije kupovine članarine</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>6d. Clan kupuje clanarinu ili odustaje</t>
-        </is>
-      </c>
-    </row>
+          <t>6d. Član kupuje članarinu ili odustaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
@@ -712,7 +715,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Clan teretane</t>
+          <t>Član teretane</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -745,7 +748,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>7d. Clan bira drugi termin ili odustaje</t>
+          <t>7d. Član bira drugi termin ili odustaje</t>
         </is>
       </c>
     </row>
